--- a/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.208</v>
+        <v>0.138</v>
+      </c>
+      <c r="E2">
+        <v>-0.155</v>
       </c>
       <c r="F2">
-        <v>0.252</v>
+        <v>0.444</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>111.5</v>
+        <v>172.4</v>
       </c>
       <c r="L2">
-        <v>0.04868783022575433</v>
+        <v>0.0735620413039768</v>
       </c>
       <c r="M2">
-        <v>42.9</v>
+        <v>49.6</v>
       </c>
       <c r="N2">
-        <v>0.01771336553945249</v>
+        <v>0.02097517655516556</v>
       </c>
       <c r="O2">
-        <v>0.3847533632286995</v>
+        <v>0.2877030162412993</v>
       </c>
       <c r="P2">
-        <v>42.9</v>
+        <v>49.6</v>
       </c>
       <c r="Q2">
-        <v>0.01771336553945249</v>
+        <v>0.02097517655516556</v>
       </c>
       <c r="R2">
-        <v>0.3847533632286995</v>
+        <v>0.2877030162412993</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1090.2</v>
+        <v>912.8</v>
       </c>
       <c r="V2">
-        <v>0.4501424501424501</v>
+        <v>0.3860109104749017</v>
       </c>
       <c r="W2">
-        <v>0.01511024379666897</v>
+        <v>0.02365013169446883</v>
       </c>
       <c r="X2">
-        <v>0.2295385017932591</v>
+        <v>0.282289064576528</v>
       </c>
       <c r="Y2">
-        <v>-0.2144282579965902</v>
+        <v>-0.2586389328820591</v>
       </c>
       <c r="Z2">
-        <v>0.1025814456633236</v>
+        <v>0.1071428571428572</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06663112260116308</v>
+        <v>0.09754046168063471</v>
       </c>
       <c r="AC2">
-        <v>-0.06663112260116308</v>
+        <v>-0.09754046168063471</v>
       </c>
       <c r="AD2">
-        <v>15844.5</v>
+        <v>14876.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15844.5</v>
+        <v>14876.9</v>
       </c>
       <c r="AG2">
-        <v>14754.3</v>
+        <v>13964.1</v>
       </c>
       <c r="AH2">
-        <v>0.8674122979897516</v>
+        <v>0.8628491555308092</v>
       </c>
       <c r="AI2">
-        <v>0.6500921112556262</v>
+        <v>0.7209966172009034</v>
       </c>
       <c r="AJ2">
-        <v>0.858996751318685</v>
+        <v>0.8551822546666014</v>
       </c>
       <c r="AK2">
-        <v>0.6337077203908514</v>
+        <v>0.7080827544242179</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.208</v>
+        <v>0.138</v>
+      </c>
+      <c r="E3">
+        <v>-0.155</v>
       </c>
       <c r="F3">
-        <v>0.252</v>
+        <v>0.444</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>111.5</v>
+        <v>172.4</v>
       </c>
       <c r="L3">
-        <v>0.04868783022575433</v>
+        <v>0.0735620413039768</v>
       </c>
       <c r="M3">
-        <v>42.9</v>
+        <v>49.6</v>
       </c>
       <c r="N3">
-        <v>0.01771336553945249</v>
+        <v>0.02097517655516556</v>
       </c>
       <c r="O3">
-        <v>0.3847533632286995</v>
+        <v>0.2877030162412993</v>
       </c>
       <c r="P3">
-        <v>42.9</v>
+        <v>49.6</v>
       </c>
       <c r="Q3">
-        <v>0.01771336553945249</v>
+        <v>0.02097517655516556</v>
       </c>
       <c r="R3">
-        <v>0.3847533632286995</v>
+        <v>0.2877030162412993</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1090.2</v>
+        <v>912.8</v>
       </c>
       <c r="V3">
-        <v>0.4501424501424501</v>
+        <v>0.3860109104749017</v>
       </c>
       <c r="W3">
-        <v>0.01511024379666897</v>
+        <v>0.02365013169446883</v>
       </c>
       <c r="X3">
-        <v>0.2295385017932591</v>
+        <v>0.282289064576528</v>
       </c>
       <c r="Y3">
-        <v>-0.2144282579965902</v>
+        <v>-0.2586389328820591</v>
       </c>
       <c r="Z3">
-        <v>0.1025814456633236</v>
+        <v>0.1071428571428572</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06663112260116308</v>
+        <v>0.09754046168063471</v>
       </c>
       <c r="AC3">
-        <v>-0.06663112260116308</v>
+        <v>-0.09754046168063471</v>
       </c>
       <c r="AD3">
-        <v>15844.5</v>
+        <v>14876.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15844.5</v>
+        <v>14876.9</v>
       </c>
       <c r="AG3">
-        <v>14754.3</v>
+        <v>13964.1</v>
       </c>
       <c r="AH3">
-        <v>0.8674122979897516</v>
+        <v>0.8628491555308092</v>
       </c>
       <c r="AI3">
-        <v>0.6500921112556262</v>
+        <v>0.7209966172009034</v>
       </c>
       <c r="AJ3">
-        <v>0.858996751318685</v>
+        <v>0.8551822546666014</v>
       </c>
       <c r="AK3">
-        <v>0.6337077203908514</v>
+        <v>0.7080827544242179</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.138</v>
+        <v>0.157</v>
       </c>
       <c r="E2">
-        <v>-0.155</v>
+        <v>0.199</v>
       </c>
       <c r="F2">
-        <v>0.444</v>
+        <v>0.338</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>172.4</v>
+        <v>813.3</v>
       </c>
       <c r="L2">
-        <v>0.0735620413039768</v>
+        <v>0.2316566024837644</v>
       </c>
       <c r="M2">
-        <v>49.6</v>
+        <v>39.2</v>
       </c>
       <c r="N2">
-        <v>0.02097517655516556</v>
+        <v>0.008551296873977444</v>
       </c>
       <c r="O2">
-        <v>0.2877030162412993</v>
+        <v>0.04819869666789623</v>
       </c>
       <c r="P2">
-        <v>49.6</v>
+        <v>39.2</v>
       </c>
       <c r="Q2">
-        <v>0.02097517655516556</v>
+        <v>0.008551296873977444</v>
       </c>
       <c r="R2">
-        <v>0.2877030162412993</v>
+        <v>0.04819869666789623</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>912.8</v>
+        <v>790</v>
       </c>
       <c r="V2">
-        <v>0.3860109104749017</v>
+        <v>0.1723348094500556</v>
       </c>
       <c r="W2">
-        <v>0.02365013169446883</v>
+        <v>0.1605503681623468</v>
       </c>
       <c r="X2">
-        <v>0.282289064576528</v>
+        <v>0.09293510939274448</v>
       </c>
       <c r="Y2">
-        <v>-0.2586389328820591</v>
+        <v>0.0676152587696023</v>
       </c>
       <c r="Z2">
-        <v>0.1071428571428572</v>
+        <v>0.184871383059951</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09754046168063471</v>
+        <v>0.06953783816169093</v>
       </c>
       <c r="AC2">
-        <v>-0.09754046168063471</v>
+        <v>-0.06953783816169093</v>
       </c>
       <c r="AD2">
-        <v>14876.9</v>
+        <v>6757.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14876.9</v>
+        <v>6757.9</v>
       </c>
       <c r="AG2">
-        <v>13964.1</v>
+        <v>5967.9</v>
       </c>
       <c r="AH2">
-        <v>0.8628491555308092</v>
+        <v>0.5958296596720155</v>
       </c>
       <c r="AI2">
-        <v>0.7209966172009034</v>
+        <v>0.4825038019691701</v>
       </c>
       <c r="AJ2">
-        <v>0.8551822546666014</v>
+        <v>0.5655705079605762</v>
       </c>
       <c r="AK2">
-        <v>0.7080827544242179</v>
+        <v>0.4515697001339296</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.138</v>
+        <v>0.157</v>
       </c>
       <c r="E3">
-        <v>-0.155</v>
+        <v>0.199</v>
       </c>
       <c r="F3">
-        <v>0.444</v>
+        <v>0.338</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>172.4</v>
+        <v>813.3</v>
       </c>
       <c r="L3">
-        <v>0.0735620413039768</v>
+        <v>0.2316566024837644</v>
       </c>
       <c r="M3">
-        <v>49.6</v>
+        <v>39.2</v>
       </c>
       <c r="N3">
-        <v>0.02097517655516556</v>
+        <v>0.008551296873977444</v>
       </c>
       <c r="O3">
-        <v>0.2877030162412993</v>
+        <v>0.04819869666789623</v>
       </c>
       <c r="P3">
-        <v>49.6</v>
+        <v>39.2</v>
       </c>
       <c r="Q3">
-        <v>0.02097517655516556</v>
+        <v>0.008551296873977444</v>
       </c>
       <c r="R3">
-        <v>0.2877030162412993</v>
+        <v>0.04819869666789623</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>912.8</v>
+        <v>790</v>
       </c>
       <c r="V3">
-        <v>0.3860109104749017</v>
+        <v>0.1723348094500556</v>
       </c>
       <c r="W3">
-        <v>0.02365013169446883</v>
+        <v>0.1605503681623468</v>
       </c>
       <c r="X3">
-        <v>0.282289064576528</v>
+        <v>0.09293510939274448</v>
       </c>
       <c r="Y3">
-        <v>-0.2586389328820591</v>
+        <v>0.0676152587696023</v>
       </c>
       <c r="Z3">
-        <v>0.1071428571428572</v>
+        <v>0.184871383059951</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09754046168063471</v>
+        <v>0.06953783816169093</v>
       </c>
       <c r="AC3">
-        <v>-0.09754046168063471</v>
+        <v>-0.06953783816169093</v>
       </c>
       <c r="AD3">
-        <v>14876.9</v>
+        <v>6757.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14876.9</v>
+        <v>6757.9</v>
       </c>
       <c r="AG3">
-        <v>13964.1</v>
+        <v>5967.9</v>
       </c>
       <c r="AH3">
-        <v>0.8628491555308092</v>
+        <v>0.5958296596720155</v>
       </c>
       <c r="AI3">
-        <v>0.7209966172009034</v>
+        <v>0.4825038019691701</v>
       </c>
       <c r="AJ3">
-        <v>0.8551822546666014</v>
+        <v>0.5655705079605762</v>
       </c>
       <c r="AK3">
-        <v>0.7080827544242179</v>
+        <v>0.4515697001339296</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.157</v>
+        <v>0.134</v>
       </c>
       <c r="E2">
-        <v>0.199</v>
+        <v>0.24</v>
       </c>
       <c r="F2">
-        <v>0.338</v>
+        <v>0.0467</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>813.3</v>
+        <v>1025.5</v>
       </c>
       <c r="L2">
-        <v>0.2316566024837644</v>
+        <v>0.2668210438674091</v>
       </c>
       <c r="M2">
-        <v>39.2</v>
+        <v>771.4000000000001</v>
       </c>
       <c r="N2">
-        <v>0.008551296873977444</v>
+        <v>0.1060868608521055</v>
       </c>
       <c r="O2">
-        <v>0.04819869666789623</v>
+        <v>0.7522184300341298</v>
       </c>
       <c r="P2">
-        <v>39.2</v>
+        <v>325.3</v>
       </c>
       <c r="Q2">
-        <v>0.008551296873977444</v>
+        <v>0.04473691448689386</v>
       </c>
       <c r="R2">
-        <v>0.04819869666789623</v>
+        <v>0.3172111165285227</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>446.1000000000001</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5782991962665284</v>
       </c>
       <c r="U2">
-        <v>790</v>
+        <v>899.7</v>
       </c>
       <c r="V2">
-        <v>0.1723348094500556</v>
+        <v>0.1237313309679016</v>
       </c>
       <c r="W2">
-        <v>0.1605503681623468</v>
+        <v>0.1632597828509568</v>
       </c>
       <c r="X2">
-        <v>0.09293510939274448</v>
+        <v>0.08882603745990808</v>
       </c>
       <c r="Y2">
-        <v>0.0676152587696023</v>
+        <v>0.07443374539104872</v>
       </c>
       <c r="Z2">
-        <v>0.184871383059951</v>
+        <v>0.3149037279803359</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06953783816169093</v>
+        <v>0.07139182499129998</v>
       </c>
       <c r="AC2">
-        <v>-0.06953783816169093</v>
+        <v>-0.07139182499129998</v>
       </c>
       <c r="AD2">
-        <v>6757.9</v>
+        <v>7753.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6757.9</v>
+        <v>7753.6</v>
       </c>
       <c r="AG2">
-        <v>5967.9</v>
+        <v>6853.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5958296596720155</v>
+        <v>0.5160465890183028</v>
       </c>
       <c r="AI2">
-        <v>0.4825038019691701</v>
+        <v>0.4637708899070497</v>
       </c>
       <c r="AJ2">
-        <v>0.5655705079605762</v>
+        <v>0.4852215528165774</v>
       </c>
       <c r="AK2">
-        <v>0.4515697001339296</v>
+        <v>0.4332728571518879</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.157</v>
+        <v>0.134</v>
       </c>
       <c r="E3">
-        <v>0.199</v>
+        <v>0.24</v>
       </c>
       <c r="F3">
-        <v>0.338</v>
+        <v>0.0467</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>813.3</v>
+        <v>1025.5</v>
       </c>
       <c r="L3">
-        <v>0.2316566024837644</v>
+        <v>0.2668210438674091</v>
       </c>
       <c r="M3">
-        <v>39.2</v>
+        <v>771.4000000000001</v>
       </c>
       <c r="N3">
-        <v>0.008551296873977444</v>
+        <v>0.1060868608521055</v>
       </c>
       <c r="O3">
-        <v>0.04819869666789623</v>
+        <v>0.7522184300341298</v>
       </c>
       <c r="P3">
-        <v>39.2</v>
+        <v>325.3</v>
       </c>
       <c r="Q3">
-        <v>0.008551296873977444</v>
+        <v>0.04473691448689386</v>
       </c>
       <c r="R3">
-        <v>0.04819869666789623</v>
+        <v>0.3172111165285227</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>446.1000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5782991962665284</v>
       </c>
       <c r="U3">
-        <v>790</v>
+        <v>899.7</v>
       </c>
       <c r="V3">
-        <v>0.1723348094500556</v>
+        <v>0.1237313309679016</v>
       </c>
       <c r="W3">
-        <v>0.1605503681623468</v>
+        <v>0.1632597828509568</v>
       </c>
       <c r="X3">
-        <v>0.09293510939274448</v>
+        <v>0.08882603745990808</v>
       </c>
       <c r="Y3">
-        <v>0.0676152587696023</v>
+        <v>0.07443374539104872</v>
       </c>
       <c r="Z3">
-        <v>0.184871383059951</v>
+        <v>0.3149037279803359</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06953783816169093</v>
+        <v>0.07139182499129998</v>
       </c>
       <c r="AC3">
-        <v>-0.06953783816169093</v>
+        <v>-0.07139182499129998</v>
       </c>
       <c r="AD3">
-        <v>6757.9</v>
+        <v>7753.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6757.9</v>
+        <v>7753.6</v>
       </c>
       <c r="AG3">
-        <v>5967.9</v>
+        <v>6853.900000000001</v>
       </c>
       <c r="AH3">
-        <v>0.5958296596720155</v>
+        <v>0.5160465890183028</v>
       </c>
       <c r="AI3">
-        <v>0.4825038019691701</v>
+        <v>0.4637708899070497</v>
       </c>
       <c r="AJ3">
-        <v>0.5655705079605762</v>
+        <v>0.4852215528165774</v>
       </c>
       <c r="AK3">
-        <v>0.4515697001339296</v>
+        <v>0.4332728571518879</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.1632597828509568</v>
       </c>
       <c r="X2">
-        <v>0.08882603745990808</v>
+        <v>0.08881147120055355</v>
       </c>
       <c r="Y2">
-        <v>0.07443374539104872</v>
+        <v>0.07444831165040325</v>
       </c>
       <c r="Z2">
         <v>0.3149037279803359</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07139182499129998</v>
+        <v>0.0713847756004001</v>
       </c>
       <c r="AC2">
-        <v>-0.07139182499129998</v>
+        <v>-0.0713847756004001</v>
       </c>
       <c r="AD2">
         <v>7753.6</v>
@@ -773,10 +773,10 @@
         <v>0.1632597828509568</v>
       </c>
       <c r="X3">
-        <v>0.08882603745990808</v>
+        <v>0.08881147120055355</v>
       </c>
       <c r="Y3">
-        <v>0.07443374539104872</v>
+        <v>0.07444831165040325</v>
       </c>
       <c r="Z3">
         <v>0.3149037279803359</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07139182499129998</v>
+        <v>0.0713847756004001</v>
       </c>
       <c r="AC3">
-        <v>-0.07139182499129998</v>
+        <v>-0.0713847756004001</v>
       </c>
       <c r="AD3">
         <v>7753.6</v>
